--- a/Result/profitability/3115.xlsx
+++ b/Result/profitability/3115.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.24</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.13875</v>
+        <v>-0.11375</v>
       </c>
       <c r="N2" t="n">
-        <v>88.75125000000001</v>
+        <v>88.77500000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,7 +780,7 @@
         <v>-0.28</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.15125</v>
+        <v>-0.13625</v>
       </c>
       <c r="N3" t="n">
         <v>76.21625</v>
@@ -899,7 +899,7 @@
         <v>-0.36</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.18375</v>
+        <v>-0.16125</v>
       </c>
       <c r="N4" t="n">
         <v>65.60625</v>
@@ -1018,7 +1018,7 @@
         <v>-0.88</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.27375</v>
+        <v>-0.2425</v>
       </c>
       <c r="N5" t="n">
         <v>48.305</v>
@@ -1137,7 +1137,7 @@
         <v>-1.13</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.38625</v>
+        <v>-0.37875</v>
       </c>
       <c r="N6" t="n">
         <v>21.33</v>
@@ -1264,7 +1264,7 @@
         <v>-0.17</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4025</v>
+        <v>-0.3925</v>
       </c>
       <c r="N7" t="n">
         <v>8.1</v>
@@ -1391,7 +1391,7 @@
         <v>-0.44</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.45</v>
+        <v>-0.4349999999999999</v>
       </c>
       <c r="N8" t="n">
         <v>-3.0125</v>
@@ -9804,6 +9804,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3115</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3</v>
+      </c>
+      <c r="F75" t="n">
+        <v>100</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-206.26%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.10625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>99.97625000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.08695652173913</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
